--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU01/HRM/post DFS_HRM-2031-0260/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad Pos 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.87597</v>
+        <v>16.83463</v>
       </c>
       <c r="D2" t="n">
-        <v>16.36543</v>
+        <v>16.48002</v>
       </c>
       <c r="E2" t="n">
-        <v>16.52923</v>
+        <v>16.75619</v>
       </c>
       <c r="F2" t="n">
-        <v>42.52302</v>
+        <v>42.67073</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04956</v>
+        <v>0.05082</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82263</v>
+        <v>1.77293</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.63083</v>
+        <v>16.57579</v>
       </c>
       <c r="D3" t="n">
-        <v>16.35483</v>
+        <v>16.52529</v>
       </c>
       <c r="E3" t="n">
-        <v>16.41341</v>
+        <v>16.55683</v>
       </c>
       <c r="F3" t="n">
-        <v>42.02329</v>
+        <v>41.6068</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05083</v>
+        <v>0.05144</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82275</v>
+        <v>1.79725</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.82245</v>
+        <v>16.8876</v>
       </c>
       <c r="D4" t="n">
-        <v>16.72306</v>
+        <v>16.40197</v>
       </c>
       <c r="E4" t="n">
-        <v>16.35411</v>
+        <v>16.61174</v>
       </c>
       <c r="F4" t="n">
-        <v>41.08772</v>
+        <v>41.97273</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04916</v>
+        <v>0.04917</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81743</v>
+        <v>1.7971</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.51329</v>
+        <v>16.88824</v>
       </c>
       <c r="D5" t="n">
-        <v>16.83677</v>
+        <v>16.36868</v>
       </c>
       <c r="E5" t="n">
-        <v>16.326</v>
+        <v>16.75999</v>
       </c>
       <c r="F5" t="n">
-        <v>42.28716</v>
+        <v>42.40409</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05018</v>
+        <v>0.04946</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82818</v>
+        <v>1.81368</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.96761</v>
+        <v>16.81658</v>
       </c>
       <c r="D6" t="n">
-        <v>16.57394</v>
+        <v>16.46368</v>
       </c>
       <c r="E6" t="n">
-        <v>16.62233</v>
+        <v>16.57997</v>
       </c>
       <c r="F6" t="n">
-        <v>42.99155</v>
+        <v>42.3791</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04985</v>
+        <v>0.05079</v>
       </c>
       <c r="H6" t="n">
-        <v>1.82828</v>
+        <v>1.78238</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.69975</v>
+        <v>16.76625</v>
       </c>
       <c r="D7" t="n">
-        <v>16.69064</v>
+        <v>16.64299</v>
       </c>
       <c r="E7" t="n">
-        <v>16.48192</v>
+        <v>16.70823</v>
       </c>
       <c r="F7" t="n">
-        <v>42.72007</v>
+        <v>42.3101</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05062</v>
+        <v>0.04944</v>
       </c>
       <c r="H7" t="n">
-        <v>1.781</v>
+        <v>1.8345</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.77968</v>
+        <v>16.70119</v>
       </c>
       <c r="D8" t="n">
-        <v>16.34433</v>
+        <v>16.42093</v>
       </c>
       <c r="E8" t="n">
-        <v>16.6987</v>
+        <v>16.6792</v>
       </c>
       <c r="F8" t="n">
-        <v>42.01129</v>
+        <v>42.58251</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05</v>
+        <v>0.05122</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82355</v>
+        <v>1.79978</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.78711</v>
+        <v>16.90108</v>
       </c>
       <c r="D9" t="n">
-        <v>16.5715</v>
+        <v>16.34704</v>
       </c>
       <c r="E9" t="n">
-        <v>16.60836</v>
+        <v>16.56513</v>
       </c>
       <c r="F9" t="n">
-        <v>43.06289</v>
+        <v>42.09952</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04961</v>
+        <v>0.05009</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8153</v>
+        <v>1.79171</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.64259</v>
+        <v>16.91882</v>
       </c>
       <c r="D10" t="n">
-        <v>16.52533</v>
+        <v>16.71422</v>
       </c>
       <c r="E10" t="n">
-        <v>16.45058</v>
+        <v>16.71613</v>
       </c>
       <c r="F10" t="n">
-        <v>42.37075</v>
+        <v>41.66855</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05044</v>
+        <v>0.04998</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81592</v>
+        <v>1.80861</v>
       </c>
     </row>
     <row r="11">
@@ -696,12 +696,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -713,8 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
-        </is>
+          <t>Pad Pos 2</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16.94409</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.58677</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.74416</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.25197</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05027</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.84144</v>
       </c>
     </row>
     <row r="13">
@@ -723,6 +746,24 @@
           <t>Unit 8</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>16.84781</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.46802</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.73549</v>
+      </c>
+      <c r="F13" t="n">
+        <v>41.05187</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.0495</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.80322</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -730,6 +771,24 @@
           <t>Unit 9</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>16.84992</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16.4984</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.68263</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.46016</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05091</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.81612</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -737,6 +796,24 @@
           <t>Unit 4</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>16.73851</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16.42821</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.51896</v>
+      </c>
+      <c r="F15" t="n">
+        <v>41.86482</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.04939</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.78024</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -744,6 +821,24 @@
           <t>Unit 5</t>
         </is>
       </c>
+      <c r="C16" t="n">
+        <v>17.38672</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.50269</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.58299</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42.56724</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05028</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.79456</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -751,6 +846,24 @@
           <t>Unit 6</t>
         </is>
       </c>
+      <c r="C17" t="n">
+        <v>16.79948</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.41865</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.45731</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.40801</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05108</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.84137</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -758,6 +871,24 @@
           <t>Unit 1</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>16.84822</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.43069</v>
+      </c>
+      <c r="E18" t="n">
+        <v>16.54925</v>
+      </c>
+      <c r="F18" t="n">
+        <v>41.20172</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.04987</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.81521</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -765,12 +896,808 @@
           <t>Unit 2</t>
         </is>
       </c>
+      <c r="C19" t="n">
+        <v>16.96823</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.46047</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.69811</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.23583</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05043</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.84085</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
+      </c>
+      <c r="C20" t="n">
+        <v>16.5022</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.32797</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.40624</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.76474</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05098</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.82342</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SR Pad Pos 1</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15.61841</v>
+      </c>
+      <c r="D22" t="n">
+        <v>15.29594</v>
+      </c>
+      <c r="E22" t="n">
+        <v>15.60908</v>
+      </c>
+      <c r="F22" t="n">
+        <v>252.16378</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15.7997</v>
+      </c>
+      <c r="D23" t="n">
+        <v>15.44968</v>
+      </c>
+      <c r="E23" t="n">
+        <v>15.674</v>
+      </c>
+      <c r="F23" t="n">
+        <v>252.98885</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>15.69744</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15.68554</v>
+      </c>
+      <c r="E24" t="n">
+        <v>15.68974</v>
+      </c>
+      <c r="F24" t="n">
+        <v>253.86089</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15.53215</v>
+      </c>
+      <c r="D25" t="n">
+        <v>15.10693</v>
+      </c>
+      <c r="E25" t="n">
+        <v>15.49326</v>
+      </c>
+      <c r="F25" t="n">
+        <v>252.48302</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>15.67084</v>
+      </c>
+      <c r="D26" t="n">
+        <v>15.37361</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.6084</v>
+      </c>
+      <c r="F26" t="n">
+        <v>254.39833</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>15.55357</v>
+      </c>
+      <c r="D27" t="n">
+        <v>15.32804</v>
+      </c>
+      <c r="E27" t="n">
+        <v>15.51627</v>
+      </c>
+      <c r="F27" t="n">
+        <v>252.74923</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>15.71257</v>
+      </c>
+      <c r="D28" t="n">
+        <v>15.46324</v>
+      </c>
+      <c r="E28" t="n">
+        <v>15.59853</v>
+      </c>
+      <c r="F28" t="n">
+        <v>258.22735</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15.774</v>
+      </c>
+      <c r="D29" t="n">
+        <v>15.49949</v>
+      </c>
+      <c r="E29" t="n">
+        <v>15.56457</v>
+      </c>
+      <c r="F29" t="n">
+        <v>251.96003</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>15.77129</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.66291</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.74766</v>
+      </c>
+      <c r="F30" t="n">
+        <v>252.46804</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Trace Pos 1</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>16.80462</v>
+      </c>
+      <c r="D32" t="n">
+        <v>15.69755</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.44051</v>
+      </c>
+      <c r="F32" t="n">
+        <v>21.58478</v>
+      </c>
+      <c r="G32" t="n">
+        <v>33.92556</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>16.80487</v>
+      </c>
+      <c r="D33" t="n">
+        <v>15.9723</v>
+      </c>
+      <c r="E33" t="n">
+        <v>16.44447</v>
+      </c>
+      <c r="F33" t="n">
+        <v>21.30414</v>
+      </c>
+      <c r="G33" t="n">
+        <v>33.73896</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>16.41439</v>
+      </c>
+      <c r="D34" t="n">
+        <v>16.03831</v>
+      </c>
+      <c r="E34" t="n">
+        <v>16.20137</v>
+      </c>
+      <c r="F34" t="n">
+        <v>21.44935</v>
+      </c>
+      <c r="G34" t="n">
+        <v>33.98911</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>16.6636</v>
+      </c>
+      <c r="D35" t="n">
+        <v>15.80626</v>
+      </c>
+      <c r="E35" t="n">
+        <v>16.27046</v>
+      </c>
+      <c r="F35" t="n">
+        <v>21.08604</v>
+      </c>
+      <c r="G35" t="n">
+        <v>33.79856</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>16.50699</v>
+      </c>
+      <c r="D36" t="n">
+        <v>15.82789</v>
+      </c>
+      <c r="E36" t="n">
+        <v>16.03477</v>
+      </c>
+      <c r="F36" t="n">
+        <v>21.95722</v>
+      </c>
+      <c r="G36" t="n">
+        <v>33.97596</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>16.56857</v>
+      </c>
+      <c r="D37" t="n">
+        <v>15.95732</v>
+      </c>
+      <c r="E37" t="n">
+        <v>16.00938</v>
+      </c>
+      <c r="F37" t="n">
+        <v>21.31573</v>
+      </c>
+      <c r="G37" t="n">
+        <v>34.64167</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>16.824</v>
+      </c>
+      <c r="D38" t="n">
+        <v>15.61784</v>
+      </c>
+      <c r="E38" t="n">
+        <v>16.51337</v>
+      </c>
+      <c r="F38" t="n">
+        <v>21.53881</v>
+      </c>
+      <c r="G38" t="n">
+        <v>33.71368</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>16.72267</v>
+      </c>
+      <c r="D39" t="n">
+        <v>16.04014</v>
+      </c>
+      <c r="E39" t="n">
+        <v>16.20496</v>
+      </c>
+      <c r="F39" t="n">
+        <v>21.76333</v>
+      </c>
+      <c r="G39" t="n">
+        <v>34.35309</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.85631</v>
+      </c>
+      <c r="D40" t="n">
+        <v>15.73537</v>
+      </c>
+      <c r="E40" t="n">
+        <v>16.51569</v>
+      </c>
+      <c r="F40" t="n">
+        <v>21.79969</v>
+      </c>
+      <c r="G40" t="n">
+        <v>33.68638</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Via Pos 1</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.60281</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.09865</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>0.59274</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.10998</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>0.61304</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.10037</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0.59709</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.1271</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.60166</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.0974</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.60507</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.10766</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.59924</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.11332</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0.61081</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.10822</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0.60373</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.1112</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Landing Pad 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>16.689</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16.42041</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.66652</v>
+      </c>
+      <c r="F52" t="n">
+        <v>42.68425</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>16.97744</v>
+      </c>
+      <c r="D53" t="n">
+        <v>16.48187</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.55205</v>
+      </c>
+      <c r="F53" t="n">
+        <v>41.76674</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>16.70318</v>
+      </c>
+      <c r="D54" t="n">
+        <v>16.32313</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.686</v>
+      </c>
+      <c r="F54" t="n">
+        <v>42.09798</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>16.69439</v>
+      </c>
+      <c r="D55" t="n">
+        <v>16.28264</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.68021</v>
+      </c>
+      <c r="F55" t="n">
+        <v>42.40691</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>16.7352</v>
+      </c>
+      <c r="D56" t="n">
+        <v>16.48321</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.66423</v>
+      </c>
+      <c r="F56" t="n">
+        <v>42.67452</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>16.90791</v>
+      </c>
+      <c r="D57" t="n">
+        <v>16.50507</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.59368</v>
+      </c>
+      <c r="F57" t="n">
+        <v>41.66409</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16.74317</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.41937</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.46337</v>
+      </c>
+      <c r="F58" t="n">
+        <v>42.50025</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>16.34261</v>
+      </c>
+      <c r="D59" t="n">
+        <v>16.25115</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.33501</v>
+      </c>
+      <c r="F59" t="n">
+        <v>42.36549</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>16.78103</v>
+      </c>
+      <c r="D60" t="n">
+        <v>16.43115</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.69032</v>
+      </c>
+      <c r="F60" t="n">
+        <v>42.11022</v>
       </c>
     </row>
   </sheetData>
